--- a/artfynd/A 33327-2021 artfynd.xlsx
+++ b/artfynd/A 33327-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 33327-2021 artfynd.xlsx
+++ b/artfynd/A 33327-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,41 +675,44 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101512617</v>
+        <v>101512593</v>
       </c>
       <c r="B2" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80386</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229497</v>
+        <v>1152</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Grynlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Pannaria conoplea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Ach.) Bory</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -718,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>334509.3771449472</v>
+        <v>334392</v>
       </c>
       <c r="R2" t="n">
-        <v>6607101.375546953</v>
+        <v>6607125</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -751,19 +754,9 @@
           <t>2022-05-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-05-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,15 +783,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>101512597</v>
+        <v>101512587</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,27 +794,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>334391.026877877</v>
+        <v>334316</v>
       </c>
       <c r="R3" t="n">
-        <v>6607125.878831225</v>
+        <v>6607398</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,19 +854,9 @@
           <t>2022-05-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-05-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,50 +883,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>101512593</v>
+        <v>101512597</v>
       </c>
       <c r="B4" t="n">
-        <v>78521</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1152</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grynlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pannaria conoplea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bory</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -957,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>334391.026877877</v>
+        <v>334392</v>
       </c>
       <c r="R4" t="n">
-        <v>6607125.878831225</v>
+        <v>6607125</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -990,19 +955,9 @@
           <t>2022-05-09</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-05-09</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,6 +981,212 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>109616681</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Eketjärnen, NV om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>334391</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6607126</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Karlanda</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>S-Årj-0308</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-05-09</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-05-09</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jeanette Fahlstad, Jan Rees</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>101512617</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Nordväst Eketjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>334509</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6607101</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Karlanda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-05-09</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-05-09</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jan Rees</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jan Rees, Jeanette Fahlstad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
